--- a/df11_test.xlsx
+++ b/df11_test.xlsx
@@ -425,30 +425,206 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:Y52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>VB_shift</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.69307</v>
+        <v>19011</v>
       </c>
       <c r="C2" t="n">
-        <v>230.402192452496</v>
+        <v>711</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1653</v>
+      </c>
+      <c r="E2" t="n">
+        <v>9455</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4662</v>
+      </c>
+      <c r="G2" t="n">
+        <v>768</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1953</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1769</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.208</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.259</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.203</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.198</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.8187385386388398</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.236524466717887</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3.111206446827591</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.855953926758787</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.4283756996806787</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.2701837177508172</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.2526393204942706</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.026377883131129</v>
       </c>
     </row>
     <row r="3">
@@ -456,10 +632,76 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.53591</v>
+        <v>16136</v>
       </c>
       <c r="C3" t="n">
-        <v>232.0307471596491</v>
+        <v>601</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1232</v>
+      </c>
+      <c r="E3" t="n">
+        <v>7457</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3077</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1268</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1617</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1415</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.181</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.139</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.191</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.228</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.207</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.9732416246099778</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.260835276277381</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.510539534169792</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.02614968917306</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.4261862103460778</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.7238178916697322</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.2207784302776403</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.858451343476339</v>
       </c>
     </row>
     <row r="4">
@@ -467,10 +709,76 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.26489</v>
+        <v>17445</v>
       </c>
       <c r="C4" t="n">
-        <v>234.3799504871212</v>
+        <v>426</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1112</v>
+      </c>
+      <c r="E4" t="n">
+        <v>9025</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2097</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1892</v>
+      </c>
+      <c r="H4" t="n">
+        <v>997</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1389</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.193</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.080094536076635</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.168299520184541</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.174947645461761</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.101596859389723</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.2808845014068919</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.095241492893244</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.1764370794022551</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.922498365184949</v>
       </c>
     </row>
     <row r="5">
@@ -478,10 +786,76 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.14834</v>
+        <v>13242</v>
       </c>
       <c r="C5" t="n">
-        <v>236.3536112992446</v>
+        <v>509</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1030</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5840</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2516</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1160</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1038</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1071</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.216</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.149</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.202</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.259</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.8620733418170468</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.2535509828873667</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.253904280387873</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.8459382792696687</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.3305218169781744</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.8113631452395734</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.1847300018179386</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.457918151602358</v>
       </c>
     </row>
     <row r="6">
@@ -489,10 +863,76 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.11409</v>
+        <v>13628</v>
       </c>
       <c r="C6" t="n">
-        <v>237.7479897099266</v>
+        <v>326</v>
+      </c>
+      <c r="D6" t="n">
+        <v>880</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5944</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1546</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1851</v>
+      </c>
+      <c r="H6" t="n">
+        <v>936</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1033</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.178</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.204</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.237</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.9778875867766229</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.1747362484493641</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.28745634333713</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.9331782127932153</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.2374257142079833</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.315287397418849</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.1797287126907745</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.89429978432606</v>
       </c>
     </row>
     <row r="7">
@@ -500,10 +940,76 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.05698</v>
+        <v>13307</v>
       </c>
       <c r="C7" t="n">
-        <v>239.9869767806604</v>
+        <v>571</v>
+      </c>
+      <c r="D7" t="n">
+        <v>512</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5489</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1701</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1518</v>
+      </c>
+      <c r="H7" t="n">
+        <v>831</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1011</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.247</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.191</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.199</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.199</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.201</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.8693145462223121</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.3375042608738871</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.314314931706655</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.841569066075147</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.2453793733394332</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.22947980746916</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.1735736198779991</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.988864394435406</v>
       </c>
     </row>
     <row r="8">
@@ -511,10 +1017,76 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.71408</v>
+        <v>23259</v>
       </c>
       <c r="C8" t="n">
-        <v>231.4139777232628</v>
+        <v>667</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1298</v>
+      </c>
+      <c r="E8" t="n">
+        <v>13373</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2288</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3745</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1714</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2442</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.201</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.204</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.248</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.216</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.9996520484783175</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.1893719569142409</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.669565007896981</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.199051232944196</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.1788819651318194</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.419130256712434</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.1530434590572233</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.191304072864788</v>
       </c>
     </row>
     <row r="9">
@@ -522,10 +1094,76 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.58795</v>
+        <v>16042</v>
       </c>
       <c r="C9" t="n">
-        <v>232.0559348815686</v>
+        <v>385</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1046</v>
+      </c>
+      <c r="E9" t="n">
+        <v>6802</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1834</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1713</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1095</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1466</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.216</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.163</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.248</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.259</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.259</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.008213286973231</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.2677295940250368</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.282747064845051</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.9845787845341781</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.2808141230563355</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.9765084666281604</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.1703001778535196</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.029108502084489</v>
       </c>
     </row>
     <row r="10">
@@ -533,10 +1171,76 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.31811</v>
+        <v>13398</v>
       </c>
       <c r="C10" t="n">
-        <v>233.0699801272991</v>
+        <v>370</v>
+      </c>
+      <c r="D10" t="n">
+        <v>602</v>
+      </c>
+      <c r="E10" t="n">
+        <v>6727</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2157</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1549</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1113</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1026</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.218</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.192</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.251</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.253</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.121085294545261</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.2818624828134882</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.854836983675858</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.086121121457254</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.3302467108540524</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.260198068320951</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.2244508618901879</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.841198476442947</v>
       </c>
     </row>
     <row r="11">
@@ -544,10 +1248,76 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.21283</v>
+        <v>12617</v>
       </c>
       <c r="C11" t="n">
-        <v>234.8613040661997</v>
+        <v>339</v>
+      </c>
+      <c r="D11" t="n">
+        <v>623</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5639</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2075</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1316</v>
+      </c>
+      <c r="H11" t="n">
+        <v>899</v>
+      </c>
+      <c r="I11" t="n">
+        <v>890</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.248</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.8712441221859597</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.3615802808543881</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.909077714146668</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.8606208337691219</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.290555582829419</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.050226361208882</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.1775030469648815</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.479192058040679</v>
       </c>
     </row>
     <row r="12">
@@ -555,10 +1325,76 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.17951</v>
+        <v>12868</v>
       </c>
       <c r="C12" t="n">
-        <v>237.2239431324182</v>
+        <v>693</v>
+      </c>
+      <c r="D12" t="n">
+        <v>729</v>
+      </c>
+      <c r="E12" t="n">
+        <v>5932</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1557</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1684</v>
+      </c>
+      <c r="H12" t="n">
+        <v>904</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1186</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.207</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.258</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.9294645893049935</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.3154667237726845</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.440716231293928</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.869420253076872</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.2748474181741339</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.210396008580458</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.1665095038258831</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.793179271971049</v>
       </c>
     </row>
     <row r="13">
@@ -566,10 +1402,76 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.08968</v>
+        <v>17793</v>
       </c>
       <c r="C13" t="n">
-        <v>239.9255400022171</v>
+        <v>775</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1409</v>
+      </c>
+      <c r="E13" t="n">
+        <v>8671</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4398</v>
+      </c>
+      <c r="G13" t="n">
+        <v>424</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1953</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1743</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.221</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.8554015243202163</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.333579908092237</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.771279236458585</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.8834502293195243</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.4998200051469945</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.3602663007396159</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.2639313558531985</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.032271440069628</v>
       </c>
     </row>
     <row r="14">
@@ -577,10 +1479,76 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.77717</v>
+        <v>13306</v>
       </c>
       <c r="C14" t="n">
-        <v>231.520066698238</v>
+        <v>751</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1274</v>
+      </c>
+      <c r="E14" t="n">
+        <v>6620</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3767</v>
+      </c>
+      <c r="G14" t="n">
+        <v>665</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1700</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1511</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.149</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.191</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.7794415254256317</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.2979028489205254</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.936470939359464</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.8652723657282533</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.475352632652522</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.3638670511814988</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.2708484065185593</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.010844230213546</v>
       </c>
     </row>
     <row r="15">
@@ -588,10 +1556,76 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.63109</v>
+        <v>13180</v>
       </c>
       <c r="C15" t="n">
-        <v>231.9223974554338</v>
+        <v>547</v>
+      </c>
+      <c r="D15" t="n">
+        <v>872</v>
+      </c>
+      <c r="E15" t="n">
+        <v>5987</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1803</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1911</v>
+      </c>
+      <c r="H15" t="n">
+        <v>956</v>
+      </c>
+      <c r="I15" t="n">
+        <v>935</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.218</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.201</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.181</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.193</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.8532251043717268</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.2746886170587531</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.451067659908874</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.7629812496205365</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.2512948062652878</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.521352340633094</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.1738688389294965</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.711521383212231</v>
       </c>
     </row>
     <row r="16">
@@ -599,10 +1633,76 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.43529</v>
+        <v>13998</v>
       </c>
       <c r="C16" t="n">
-        <v>232.9076629013125</v>
+        <v>334</v>
+      </c>
+      <c r="D16" t="n">
+        <v>621</v>
+      </c>
+      <c r="E16" t="n">
+        <v>5773</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1795</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2105</v>
+      </c>
+      <c r="H16" t="n">
+        <v>859</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1070</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.164</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.239</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.213</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.885601618208937</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.2002329240136486</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.57442330874691</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.9267923911488875</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.2804282532742169</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.261467421285986</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.1654986412765871</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.705555442044828</v>
       </c>
     </row>
     <row r="17">
@@ -610,10 +1710,76 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.36274</v>
+        <v>12732</v>
       </c>
       <c r="C17" t="n">
-        <v>234.4329638920183</v>
+        <v>711</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1001</v>
+      </c>
+      <c r="E17" t="n">
+        <v>6149</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1785</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1607</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1082</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1208</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.203</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.218</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.179</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.199</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.251</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.7552565846306188</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.2839310468536161</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.602701262824815</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.8104940792003223</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.2813959482209946</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.277689710841273</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.1784709437365587</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.810060423691803</v>
       </c>
     </row>
     <row r="18">
@@ -621,10 +1787,76 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.21933</v>
+        <v>20552</v>
       </c>
       <c r="C18" t="n">
-        <v>236.9837480470651</v>
+        <v>867</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1550</v>
+      </c>
+      <c r="E18" t="n">
+        <v>10440</v>
+      </c>
+      <c r="F18" t="n">
+        <v>4127</v>
+      </c>
+      <c r="G18" t="n">
+        <v>539</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1576</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1745</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.181</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.164</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.199</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.8814126359445075</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.2732854060822149</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.956858492037079</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.9398411372210417</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.4032079761868744</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.2257964666646496</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.2027560108825426</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.116841874981091</v>
       </c>
     </row>
     <row r="19">
@@ -632,10 +1864,76 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.20591</v>
+        <v>17992</v>
       </c>
       <c r="C19" t="n">
-        <v>238.8175999071128</v>
+        <v>722</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1597</v>
+      </c>
+      <c r="E19" t="n">
+        <v>8610</v>
+      </c>
+      <c r="F19" t="n">
+        <v>4165</v>
+      </c>
+      <c r="G19" t="n">
+        <v>446</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1748</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1441</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.199</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.173</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.169</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.8535463001697753</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.2781048802187803</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.913030779240783</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.8823937894399266</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.4590750655911706</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.3393822267076641</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.2593849875551433</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.015081971076755</v>
       </c>
     </row>
     <row r="20">
@@ -643,10 +1941,76 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.79499</v>
+        <v>17421</v>
       </c>
       <c r="C20" t="n">
-        <v>230.9396315944537</v>
+        <v>755</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1484</v>
+      </c>
+      <c r="E20" t="n">
+        <v>7594</v>
+      </c>
+      <c r="F20" t="n">
+        <v>4466</v>
+      </c>
+      <c r="G20" t="n">
+        <v>587</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2021</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1501</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.207</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.179</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.8100037298810614</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.3509631545662243</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.057706387727654</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.8244793210133569</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.477509066951404</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.2423088080840782</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.3115398961081006</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.925489635668121</v>
       </c>
     </row>
     <row r="21">
@@ -654,10 +2018,76 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>-0.65326</v>
+        <v>19915</v>
       </c>
       <c r="C21" t="n">
-        <v>231.0448528024583</v>
+        <v>910</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1436</v>
+      </c>
+      <c r="E21" t="n">
+        <v>9352</v>
+      </c>
+      <c r="F21" t="n">
+        <v>4266</v>
+      </c>
+      <c r="G21" t="n">
+        <v>377</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1573</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1582</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.173</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.189</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.9177610591642946</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.2840620212500964</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.946541644153543</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.9406873591228154</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.4255771807469664</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.2253237727882121</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.2451324561102527</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>2.01491450666382</v>
       </c>
     </row>
     <row r="22">
@@ -665,10 +2095,76 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.50854</v>
+        <v>18838</v>
       </c>
       <c r="C22" t="n">
-        <v>232.179908827496</v>
+        <v>977</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1421</v>
+      </c>
+      <c r="E22" t="n">
+        <v>9553</v>
+      </c>
+      <c r="F22" t="n">
+        <v>3955</v>
+      </c>
+      <c r="G22" t="n">
+        <v>517</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1787</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1554</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.192</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.198</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.213</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.203</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.8036671295906863</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.225288950700753</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.096699031450351</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.8579599048174131</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.3989369925720477</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.1990735091646654</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0.2064466020966901</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.211927879607393</v>
       </c>
     </row>
     <row r="23">
@@ -676,10 +2172,76 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>-0.44227</v>
+        <v>18600</v>
       </c>
       <c r="C23" t="n">
-        <v>233.7670271377276</v>
+        <v>2046</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3989</v>
+      </c>
+      <c r="E23" t="n">
+        <v>11646</v>
+      </c>
+      <c r="F23" t="n">
+        <v>10819</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1069</v>
+      </c>
+      <c r="H23" t="n">
+        <v>5604</v>
+      </c>
+      <c r="I23" t="n">
+        <v>4759</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.3877143835577986</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.322107260550057</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.0590309161441</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.5807631633609728</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.4998873195609232</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.2525479012165477</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0.3546849799781697</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>2.543264075631432</v>
       </c>
     </row>
     <row r="24">
@@ -687,10 +2249,76 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>-0.29445</v>
+        <v>24561</v>
       </c>
       <c r="C24" t="n">
-        <v>236.5258901983055</v>
+        <v>2533</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3179</v>
+      </c>
+      <c r="E24" t="n">
+        <v>14812</v>
+      </c>
+      <c r="F24" t="n">
+        <v>10567</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1114</v>
+      </c>
+      <c r="H24" t="n">
+        <v>6250</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3648</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.211</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.201</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.6722732176637873</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.4002416038324634</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.865818334623605</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.8865220858368474</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0.5259686427632607</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.2627000140071638</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0.3764229637938148</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2.010053137479056</v>
       </c>
     </row>
     <row r="25">
@@ -698,10 +2326,76 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>-0.21884</v>
+        <v>23331</v>
       </c>
       <c r="C25" t="n">
-        <v>237.582160733056</v>
+        <v>1843</v>
+      </c>
+      <c r="D25" t="n">
+        <v>3664</v>
+      </c>
+      <c r="E25" t="n">
+        <v>13544</v>
+      </c>
+      <c r="F25" t="n">
+        <v>7251</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2490</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3982</v>
+      </c>
+      <c r="I25" t="n">
+        <v>3366</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.204</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.196</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.163</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.196</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.201</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.249</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.5903138450612492</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.3016540874919906</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.217643599914567</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.7821911583358748</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.3406039284593629</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.6404348319060722</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0.2360194618618652</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.891139086969018</v>
       </c>
     </row>
     <row r="26">
@@ -709,10 +2403,76 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>-0.92685</v>
+        <v>31399</v>
       </c>
       <c r="C26" t="n">
-        <v>229.8459023014056</v>
+        <v>3103</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1461</v>
+      </c>
+      <c r="E26" t="n">
+        <v>20888</v>
+      </c>
+      <c r="F26" t="n">
+        <v>6393</v>
+      </c>
+      <c r="G26" t="n">
+        <v>3366</v>
+      </c>
+      <c r="H26" t="n">
+        <v>8582</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3440</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.187</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.247</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.039937524050597</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.6023003805711884</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.349359650893392</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.404349229142966</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.3439870045996701</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.884063219550843</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.5729793197389674</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.803023671452377</v>
       </c>
     </row>
     <row r="27">
@@ -720,10 +2480,76 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>-0.7688199999999999</v>
+        <v>40676</v>
       </c>
       <c r="C27" t="n">
-        <v>230.4648547122869</v>
+        <v>1702</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1259</v>
+      </c>
+      <c r="E27" t="n">
+        <v>28955</v>
+      </c>
+      <c r="F27" t="n">
+        <v>4940</v>
+      </c>
+      <c r="G27" t="n">
+        <v>4021</v>
+      </c>
+      <c r="H27" t="n">
+        <v>4571</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3440</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.171</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.178</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.216812723878142</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.2991374949241055</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.244586657713431</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.673581982219056</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.2259907352163862</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.9864986876402251</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0.2605209966221198</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>2.092870721786533</v>
       </c>
     </row>
     <row r="28">
@@ -731,10 +2557,76 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>-0.61721</v>
+        <v>29415</v>
       </c>
       <c r="C28" t="n">
-        <v>231.4625126664563</v>
+        <v>5686</v>
+      </c>
+      <c r="D28" t="n">
+        <v>938</v>
+      </c>
+      <c r="E28" t="n">
+        <v>19944</v>
+      </c>
+      <c r="F28" t="n">
+        <v>6241</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2875</v>
+      </c>
+      <c r="H28" t="n">
+        <v>15891</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2848</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.171</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.196</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.9843937928250793</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1.191728330500775</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0.9586210306885351</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.302924560339708</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.3190726322871382</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.7684683344372026</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.072218745332188</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.402572573589373</v>
       </c>
     </row>
     <row r="29">
@@ -742,10 +2634,76 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>-0.5518</v>
+        <v>21451</v>
       </c>
       <c r="C29" t="n">
-        <v>233.1414978506785</v>
+        <v>1605</v>
+      </c>
+      <c r="D29" t="n">
+        <v>4713</v>
+      </c>
+      <c r="E29" t="n">
+        <v>10756</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4663</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1647</v>
+      </c>
+      <c r="H29" t="n">
+        <v>3918</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2404</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.5350885206753618</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.276705454437294</v>
+      </c>
+      <c r="T29" t="n">
+        <v>4.273977492186853</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0.5971942780779338</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0.2487945278072774</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.3903790465304526</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0.264419304915947</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.41344137536888</v>
       </c>
     </row>
     <row r="30">
@@ -753,10 +2711,76 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>-0.41453</v>
+        <v>18671</v>
       </c>
       <c r="C30" t="n">
-        <v>235.8525967052367</v>
+        <v>1105</v>
+      </c>
+      <c r="D30" t="n">
+        <v>4919</v>
+      </c>
+      <c r="E30" t="n">
+        <v>8942</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3888</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1294</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2762</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1726</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.4732806581589791</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.2060671039459676</v>
+      </c>
+      <c r="T30" t="n">
+        <v>4.76728319321152</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0.5194187945267413</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0.2088976960331375</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0.3174225966552309</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0.205840656578994</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.30178930088943</v>
       </c>
     </row>
     <row r="31">
@@ -764,10 +2788,76 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>-0.31288</v>
+        <v>13880</v>
       </c>
       <c r="C31" t="n">
-        <v>237.4277214461427</v>
+        <v>743</v>
+      </c>
+      <c r="D31" t="n">
+        <v>4015</v>
+      </c>
+      <c r="E31" t="n">
+        <v>5831</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2781</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1425</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1291</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1520</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.169</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.169</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.163</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.4441993738100332</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.1811482939056828</v>
+      </c>
+      <c r="T31" t="n">
+        <v>4.703916353222976</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0.4363757112803959</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0.1909056961535298</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0.5024637922760905</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0.1511973113535957</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.389793467997697</v>
       </c>
     </row>
     <row r="32">
@@ -775,10 +2865,76 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>-1.07251</v>
+        <v>13539</v>
       </c>
       <c r="C32" t="n">
-        <v>230.375773978929</v>
+        <v>567</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2327</v>
+      </c>
+      <c r="E32" t="n">
+        <v>6489</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2977</v>
+      </c>
+      <c r="G32" t="n">
+        <v>942</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1583</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1152</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.6580357341325066</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.1932701528963455</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3.98988213945337</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0.6861239326243144</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0.3011364246702139</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0.495295713863177</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0.2611252913224233</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.415130611037648</v>
       </c>
     </row>
     <row r="33">
@@ -786,10 +2942,76 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>-0.92081</v>
+        <v>13109</v>
       </c>
       <c r="C33" t="n">
-        <v>230.9685366278752</v>
+        <v>688</v>
+      </c>
+      <c r="D33" t="n">
+        <v>3046</v>
+      </c>
+      <c r="E33" t="n">
+        <v>6136</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2455</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1634</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1358</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1299</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.164</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.178</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.5050929002667666</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0.16144521926335</v>
+      </c>
+      <c r="T33" t="n">
+        <v>4.013066878831844</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0.5384302896990686</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0.2026302241774699</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0.768017971638508</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0.1680348200496092</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.643281696073384</v>
       </c>
     </row>
     <row r="34">
@@ -797,10 +3019,76 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>-0.75036</v>
+        <v>17090</v>
       </c>
       <c r="C34" t="n">
-        <v>231.2244404514734</v>
+        <v>1503</v>
+      </c>
+      <c r="D34" t="n">
+        <v>4244</v>
+      </c>
+      <c r="E34" t="n">
+        <v>9912</v>
+      </c>
+      <c r="F34" t="n">
+        <v>8315</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1414</v>
+      </c>
+      <c r="H34" t="n">
+        <v>4349</v>
+      </c>
+      <c r="I34" t="n">
+        <v>3646</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.3587772044663293</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0.252686562590603</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3.699783849274351</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0.4616244068819374</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0.3836767982619044</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0.3462183051614531</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0.2909397522365152</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>2.206293121126907</v>
       </c>
     </row>
     <row r="35">
@@ -808,10 +3096,76 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>-0.5654</v>
+        <v>23236</v>
       </c>
       <c r="C35" t="n">
-        <v>232.8890493260791</v>
+        <v>2612</v>
+      </c>
+      <c r="D35" t="n">
+        <v>3038</v>
+      </c>
+      <c r="E35" t="n">
+        <v>13888</v>
+      </c>
+      <c r="F35" t="n">
+        <v>11616</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1053</v>
+      </c>
+      <c r="H35" t="n">
+        <v>7303</v>
+      </c>
+      <c r="I35" t="n">
+        <v>4004</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.212</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.6184264907669164</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0.4135187113910519</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.752676795229987</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0.7924746648150903</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0.5706822728099323</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0.251814379473954</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0.4062887467142787</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>2.19411793879879</v>
       </c>
     </row>
     <row r="36">
@@ -819,10 +3173,76 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>-0.45231</v>
+        <v>18326</v>
       </c>
       <c r="C36" t="n">
-        <v>235.2603696605706</v>
+        <v>1604</v>
+      </c>
+      <c r="D36" t="n">
+        <v>3595</v>
+      </c>
+      <c r="E36" t="n">
+        <v>11264</v>
+      </c>
+      <c r="F36" t="n">
+        <v>8238</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2516</v>
+      </c>
+      <c r="H36" t="n">
+        <v>4770</v>
+      </c>
+      <c r="I36" t="n">
+        <v>3624</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.198</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.203</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.4280515857868815</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0.3044660487329904</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3.335287170211394</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0.572194871751091</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0.3662489319986134</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0.6352268925838298</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0.2929991455988908</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>2.06552535333631</v>
       </c>
     </row>
     <row r="37">
@@ -830,10 +3250,76 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>-0.35132</v>
+        <v>23152</v>
       </c>
       <c r="C37" t="n">
-        <v>236.6518888592141</v>
+        <v>4673</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1014</v>
+      </c>
+      <c r="E37" t="n">
+        <v>16269</v>
+      </c>
+      <c r="F37" t="n">
+        <v>7200</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2964</v>
+      </c>
+      <c r="H37" t="n">
+        <v>14711</v>
+      </c>
+      <c r="I37" t="n">
+        <v>3389</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.179</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.223</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.872197607017039</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0.5134913051980355</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1.038330484544094</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.154078800853927</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0.4085234693288238</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0.8987516325234126</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0.9571121281418161</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>2.157514572392851</v>
       </c>
     </row>
     <row r="38">
@@ -841,10 +3327,76 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>-1.15665</v>
+        <v>19079</v>
       </c>
       <c r="C38" t="n">
-        <v>230.4402718200508</v>
+        <v>1822</v>
+      </c>
+      <c r="D38" t="n">
+        <v>3324</v>
+      </c>
+      <c r="E38" t="n">
+        <v>11189</v>
+      </c>
+      <c r="F38" t="n">
+        <v>5141</v>
+      </c>
+      <c r="G38" t="n">
+        <v>5460</v>
+      </c>
+      <c r="H38" t="n">
+        <v>4203</v>
+      </c>
+      <c r="I38" t="n">
+        <v>3441</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.139</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.181</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0.204</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.5205639107824286</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0.316044290478354</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.662564912934078</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0.6482253380047932</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0.2650968375856839</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.429992180068498</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0.3261873949085791</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.831325135237586</v>
       </c>
     </row>
     <row r="39">
@@ -852,10 +3404,76 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>-1.01677</v>
+        <v>15728</v>
       </c>
       <c r="C39" t="n">
-        <v>230.7929716398503</v>
+        <v>949</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2945</v>
+      </c>
+      <c r="E39" t="n">
+        <v>7202</v>
+      </c>
+      <c r="F39" t="n">
+        <v>3416</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1167</v>
+      </c>
+      <c r="H39" t="n">
+        <v>2489</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1801</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.169</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0.5349839445821997</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0.251730227372653</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3.810280259776976</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0.6103937910011273</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0.277679690746295</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0.4994556556734684</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0.2648071223011026</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.750669308546178</v>
       </c>
     </row>
     <row r="40">
@@ -863,10 +3481,76 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>-0.88145</v>
+        <v>20753</v>
       </c>
       <c r="C40" t="n">
-        <v>231.0553614407679</v>
+        <v>1133</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1220</v>
+      </c>
+      <c r="E40" t="n">
+        <v>11366</v>
+      </c>
+      <c r="F40" t="n">
+        <v>3606</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2427</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1452</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1903</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.247</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.178</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.216</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.212</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0.9434018928319301</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0.2371758677631294</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1.813697812306284</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.083652734849293</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0.2855079248493134</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.36445881571965</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0.1793767067116105</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>2.092728244968789</v>
       </c>
     </row>
     <row r="41">
@@ -874,10 +3558,76 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>-0.7537700000000001</v>
+        <v>16430</v>
       </c>
       <c r="C41" t="n">
-        <v>233.3740384442591</v>
+        <v>787</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1117</v>
+      </c>
+      <c r="E41" t="n">
+        <v>9161</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2285</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2322</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1114</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1575</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.189</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0.9039533985406958</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0.3223206274989829</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1.965116083784121</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.05316610897175</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0.2991120569705422</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.384938954285952</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0.1764594034418395</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.894933366506117</v>
       </c>
     </row>
     <row r="42">
@@ -885,10 +3635,76 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>-0.65738</v>
+        <v>16074</v>
       </c>
       <c r="C42" t="n">
-        <v>235.1531274027425</v>
+        <v>542</v>
+      </c>
+      <c r="D42" t="n">
+        <v>993</v>
+      </c>
+      <c r="E42" t="n">
+        <v>7569</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2384</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2054</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1243</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1409</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.208</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0.207</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0.187</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0.8990297009806183</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0.238976528702982</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1.935709882494155</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0.9795865162924963</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0.2995741484812381</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.182933817079761</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0.2058612097255688</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>2.25832819624318</v>
       </c>
     </row>
     <row r="43">
@@ -896,10 +3712,76 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>-0.61352</v>
+        <v>15978</v>
       </c>
       <c r="C43" t="n">
-        <v>236.0397675733168</v>
+        <v>2049</v>
+      </c>
+      <c r="D43" t="n">
+        <v>7487</v>
+      </c>
+      <c r="E43" t="n">
+        <v>9848</v>
+      </c>
+      <c r="F43" t="n">
+        <v>10529</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1540</v>
+      </c>
+      <c r="H43" t="n">
+        <v>7125</v>
+      </c>
+      <c r="I43" t="n">
+        <v>5341</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0.2004659794505527</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0.2068730175674474</v>
+      </c>
+      <c r="T43" t="n">
+        <v>4.284079091955004</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0.3023669171153512</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0.3318289109802399</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0.231376423531747</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0.3145273257384686</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>2.128482333661189</v>
       </c>
     </row>
     <row r="44">
@@ -907,10 +3789,76 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>-1.54332</v>
+        <v>18643</v>
       </c>
       <c r="C44" t="n">
-        <v>227.9933548386791</v>
+        <v>1499</v>
+      </c>
+      <c r="D44" t="n">
+        <v>3628</v>
+      </c>
+      <c r="E44" t="n">
+        <v>13520</v>
+      </c>
+      <c r="F44" t="n">
+        <v>8424</v>
+      </c>
+      <c r="G44" t="n">
+        <v>5514</v>
+      </c>
+      <c r="H44" t="n">
+        <v>5052</v>
+      </c>
+      <c r="I44" t="n">
+        <v>5303</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0.3687417183237082</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0.2026197981226399</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2.857728581314116</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0.6036969569566637</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0.3383261935257438</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.191246527404144</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0.2706609548205951</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>2.166979269532389</v>
       </c>
     </row>
     <row r="45">
@@ -918,10 +3866,76 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>-1.39168</v>
+        <v>12598</v>
       </c>
       <c r="C45" t="n">
-        <v>229.7401463998891</v>
+        <v>560</v>
+      </c>
+      <c r="D45" t="n">
+        <v>2853</v>
+      </c>
+      <c r="E45" t="n">
+        <v>6851</v>
+      </c>
+      <c r="F45" t="n">
+        <v>3016</v>
+      </c>
+      <c r="G45" t="n">
+        <v>5979</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1652</v>
+      </c>
+      <c r="I45" t="n">
+        <v>2510</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0.173</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0.4106578074967073</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0.1387675294519229</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.921174094564206</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0.5118789915376013</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0.1958033360486877</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.947449396376137</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0.1596666585848759</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.71460218593986</v>
       </c>
     </row>
     <row r="46">
@@ -929,10 +3943,76 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>-1.29899</v>
+        <v>9765</v>
       </c>
       <c r="C46" t="n">
-        <v>230.3707978027688</v>
+        <v>707</v>
+      </c>
+      <c r="D46" t="n">
+        <v>4041</v>
+      </c>
+      <c r="E46" t="n">
+        <v>5304</v>
+      </c>
+      <c r="F46" t="n">
+        <v>2499</v>
+      </c>
+      <c r="G46" t="n">
+        <v>8400</v>
+      </c>
+      <c r="H46" t="n">
+        <v>2119</v>
+      </c>
+      <c r="I46" t="n">
+        <v>4012</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0.2086636639643324</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0.109788990634282</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3.235546135751486</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0.2943166898661259</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0.1245505355935132</v>
+      </c>
+      <c r="W46" t="n">
+        <v>2.005263623055562</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0.1328539046330807</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.889016456501617</v>
       </c>
     </row>
     <row r="47">
@@ -940,10 +4020,76 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>-1.27164</v>
+        <v>9773</v>
       </c>
       <c r="C47" t="n">
-        <v>232.0036692262959</v>
+        <v>739</v>
+      </c>
+      <c r="D47" t="n">
+        <v>2737</v>
+      </c>
+      <c r="E47" t="n">
+        <v>5175</v>
+      </c>
+      <c r="F47" t="n">
+        <v>2524</v>
+      </c>
+      <c r="G47" t="n">
+        <v>7806</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1529</v>
+      </c>
+      <c r="I47" t="n">
+        <v>2445</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0.3060266717195751</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0.1427041884526078</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2.686775410176684</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0.3800673307502682</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0.1676598470243692</v>
+      </c>
+      <c r="W47" t="n">
+        <v>2.426955370511246</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0.1404546642996603</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1.749356517065588</v>
       </c>
     </row>
     <row r="48">
@@ -951,10 +4097,76 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>-1.22656</v>
+        <v>21363</v>
       </c>
       <c r="C48" t="n">
-        <v>233.5190227978792</v>
+        <v>1970</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1909</v>
+      </c>
+      <c r="E48" t="n">
+        <v>12601</v>
+      </c>
+      <c r="F48" t="n">
+        <v>5040</v>
+      </c>
+      <c r="G48" t="n">
+        <v>3447</v>
+      </c>
+      <c r="H48" t="n">
+        <v>4543</v>
+      </c>
+      <c r="I48" t="n">
+        <v>2710</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0.127</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0.6985278838148835</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0.4008136779435319</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2.154663124205114</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0.8606015176443884</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0.3150077770295263</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.096793035482474</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0.3884351217461016</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>2.085157862133981</v>
       </c>
     </row>
     <row r="49">
@@ -962,10 +4174,307 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>-1.20057</v>
+        <v>10356</v>
       </c>
       <c r="C49" t="n">
-        <v>234.8381800496444</v>
+        <v>789</v>
+      </c>
+      <c r="D49" t="n">
+        <v>3145</v>
+      </c>
+      <c r="E49" t="n">
+        <v>5331</v>
+      </c>
+      <c r="F49" t="n">
+        <v>2925</v>
+      </c>
+      <c r="G49" t="n">
+        <v>7463</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1709</v>
+      </c>
+      <c r="I49" t="n">
+        <v>2949</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0.173</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0.2778336205591168</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0.151020673045723</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2.784998882343186</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0.3445209578679433</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0.1499102269203867</v>
+      </c>
+      <c r="W49" t="n">
+        <v>2.262645024985038</v>
+      </c>
+      <c r="X49" t="n">
+        <v>0.1302077399537074</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>1.898862874324899</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" t="n">
+        <v>27699</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1445</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1368</v>
+      </c>
+      <c r="E50" t="n">
+        <v>15881</v>
+      </c>
+      <c r="F50" t="n">
+        <v>5387</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1369</v>
+      </c>
+      <c r="H50" t="n">
+        <v>3089</v>
+      </c>
+      <c r="I50" t="n">
+        <v>2007</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.198</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1.178711741080651</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0.4078004250893772</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1.557056168523077</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1.347855469611712</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0.3921528290853575</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0.6855091443237962</v>
+      </c>
+      <c r="X50" t="n">
+        <v>0.3379880736868275</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>2.092926148599201</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" t="n">
+        <v>22769</v>
+      </c>
+      <c r="C51" t="n">
+        <v>1299</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1236</v>
+      </c>
+      <c r="E51" t="n">
+        <v>12034</v>
+      </c>
+      <c r="F51" t="n">
+        <v>4534</v>
+      </c>
+      <c r="G51" t="n">
+        <v>1204</v>
+      </c>
+      <c r="H51" t="n">
+        <v>2784</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1790</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0.212</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1.120979635196427</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0.458836644606709</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2.077278627401283</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1.182205886963534</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0.3660265051294429</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0.5856424082071086</v>
+      </c>
+      <c r="X51" t="n">
+        <v>0.3132007018250471</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1.895829590670448</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" t="n">
+        <v>20626</v>
+      </c>
+      <c r="C52" t="n">
+        <v>984</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1152</v>
+      </c>
+      <c r="E52" t="n">
+        <v>9746</v>
+      </c>
+      <c r="F52" t="n">
+        <v>3791</v>
+      </c>
+      <c r="G52" t="n">
+        <v>1270</v>
+      </c>
+      <c r="H52" t="n">
+        <v>2021</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1190</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0.169</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0.218</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1.084509203370883</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0.3682543984281437</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2.332277856711576</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1.128197566093494</v>
+      </c>
+      <c r="V52" t="n">
+        <v>0.3945582840301538</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0.7641278767383979</v>
+      </c>
+      <c r="X52" t="n">
+        <v>0.2709300217007057</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>1.657144792926646</v>
       </c>
     </row>
   </sheetData>
